--- a/sales.xlsx
+++ b/sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,52 +441,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:51</t>
+          <t>2026-04-29 10:20:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-18 20:10:43</t>
+          <t>2026-04-29 10:28:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>biscuits</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-18 20:17:40</t>
+          <t>2026-04-29 10:29:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>100</v>
@@ -495,702 +495,324 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-18 20:17:59</t>
+          <t>2026-04-29 11:58:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>pipe biscuit pockets</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-18 20:21:51</t>
+          <t>2026-04-29 14:11:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>colgate</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-18 20:55:59</t>
+          <t>2026-04-29 14:43:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
         <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-18 20:56:03</t>
+          <t>2026-04-29 15:31:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-18 20:56:04</t>
+          <t>2026-04-29 15:55:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>ps5</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-18 20:56:04</t>
+          <t>2026-04-29 15:57:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>cookies</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-18 20:56:05</t>
+          <t>2026-04-29 16:02:48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-18 20:56:15</t>
+          <t>2026-04-29 16:03:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-18 20:57:33</t>
+          <t>2026-04-29 16:04:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>45000</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-26 21:35:24</t>
+          <t>2026-04-29 16:04:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>mobiles</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-26 21:50:36</t>
+          <t>2026-04-29 16:15:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>pineapple</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-26 22:02:16</t>
+          <t>2026-04-29 16:15:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-26 22:04:58</t>
+          <t>2026-04-29 16:16:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>laptops</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-26 22:42:21</t>
+          <t>2026-04-29 16:17:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>120</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-27 19:10:42</t>
+          <t>2026-04-29 16:28:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-27 19:13:54</t>
+          <t>2026-04-29 19:51:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>biscuits</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-27 19:14:21</t>
+          <t>2026-04-29 21:47:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>Iphone</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-27 19:20:05</t>
+          <t>2026-04-29 21:47:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bro</t>
+          <t>Biscuits</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-04-27 19:20:50</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bro</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-04-27 19:26:31</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>biscuitassumingbiscuitpacketsistheproductinthiscontext</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:43:40</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:44:50</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>biscuitproductname</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:51:18</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:53:40</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>biscuit packets</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:55:23</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>milk bottles</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:56:08</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>rice bags</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-04-28 19:56:42</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>chocolate bars</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-04-28 20:11:01</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>five</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>120</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-04-28 20:11:36</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>biscuits</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-04-28 20:15:47</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>biscuits</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-04-28 20:19:02</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>apples</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-04-28 21:15:33</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>cookies</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-04-29 10:20:13</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>500</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-04-29 10:28:42</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>100</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-04-29 10:29:08</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-04-29 11:58:08</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>pipe biscuit pockets</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-04-29 14:11:30</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>colgate</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-04-29 14:43:32</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-04-29 15:31:15</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
         <v>20</v>
       </c>
     </row>
